--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/5mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/5mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.64511791667</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>729.5776396341751</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>719.7754354170587</v>
+        <v>0.250641182</v>
+      </c>
+      <c r="Y2">
+        <v>0.261928438</v>
+      </c>
+      <c r="Z2">
+        <v>0.3625293212244728</v>
+      </c>
+      <c r="AA2">
+        <v>5.643628</v>
+      </c>
+      <c r="AB2">
+        <v>0.06501063621951469</v>
+      </c>
+      <c r="AC2">
+        <v>47.43030652414954</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.64523423611</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>710.2383870798124</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>719.7754354170587</v>
+      </c>
+      <c r="X3">
+        <v>0.250666922</v>
+      </c>
+      <c r="Y3">
+        <v>0.261935124</v>
+      </c>
+      <c r="Z3">
+        <v>0.3625519479603571</v>
+      </c>
+      <c r="AA3">
+        <v>5.634101000000001</v>
+      </c>
+      <c r="AB3">
+        <v>0.06512193565147807</v>
+      </c>
+      <c r="AC3">
+        <v>46.25209854062111</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.64535055555</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>724.1014407635927</v>
       </c>
-      <c r="V4">
-        <v>9.968113335957543</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.250695522</v>
+      </c>
+      <c r="Y4">
+        <v>0.261934168</v>
+      </c>
+      <c r="Z4">
+        <v>0.362571031822324</v>
+      </c>
+      <c r="AA4">
+        <v>5.619323000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.06529251970733432</v>
+      </c>
+      <c r="AC4">
+        <v>47.27840759116605</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.645466875</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>718.8692630168357</v>
       </c>
-      <c r="V5">
-        <v>7.000618554257914</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>46.98556742134338</v>
+      </c>
+      <c r="X5">
+        <v>0.250712682</v>
+      </c>
+      <c r="Y5">
+        <v>0.261938306</v>
+      </c>
+      <c r="Z5">
+        <v>0.3625858864679963</v>
+      </c>
+      <c r="AA5">
+        <v>5.612811999999998</v>
+      </c>
+      <c r="AB5">
+        <v>0.06536910039210496</v>
+      </c>
+      <c r="AC5">
+        <v>46.99183702294604</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.64558261574</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>710.8120626665743</v>
       </c>
-      <c r="V6">
-        <v>6.694546681982043</v>
-      </c>
-      <c r="W6" t="b">
-        <v>0</v>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.250727936</v>
+      </c>
+      <c r="Y6">
+        <v>0.261940534</v>
+      </c>
+      <c r="Z6">
+        <v>0.3625980436282375</v>
+      </c>
+      <c r="AA6">
+        <v>5.606299</v>
+      </c>
+      <c r="AB6">
+        <v>0.06544540841111696</v>
+      </c>
+      <c r="AC6">
+        <v>46.51938574476242</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.64569835648</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>727.0286026225377</v>
       </c>
-      <c r="V7">
-        <v>8.108323587819998</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.250718402</v>
+      </c>
+      <c r="Y7">
+        <v>0.261940852</v>
+      </c>
+      <c r="Z7">
+        <v>0.3625916808862547</v>
+      </c>
+      <c r="AA7">
+        <v>5.611225000000005</v>
+      </c>
+      <c r="AB7">
+        <v>0.06538817636927462</v>
+      </c>
+      <c r="AC7">
+        <v>47.53907449378977</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.64581409722</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>712.963110163048</v>
       </c>
-      <c r="V8">
-        <v>8.807584341571797</v>
-      </c>
-      <c r="W8" t="b">
-        <v>0</v>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.250706962</v>
+      </c>
+      <c r="Y8">
+        <v>0.2619434</v>
+      </c>
+      <c r="Z8">
+        <v>0.3625856114062297</v>
+      </c>
+      <c r="AA8">
+        <v>5.618218999999996</v>
+      </c>
+      <c r="AB8">
+        <v>0.0653076134402832</v>
+      </c>
+      <c r="AC8">
+        <v>46.56191919571038</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.64593041666</v>
       </c>
@@ -1056,11 +1212,26 @@
       <c r="U9">
         <v>724.6129773898936</v>
       </c>
-      <c r="V9">
-        <v>7.521000928463391</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.250708552</v>
+      </c>
+      <c r="Y9">
+        <v>0.261947856</v>
+      </c>
+      <c r="Z9">
+        <v>0.3625899299607387</v>
+      </c>
+      <c r="AA9">
+        <v>5.619652000000002</v>
+      </c>
+      <c r="AB9">
+        <v>0.06529211004199933</v>
+      </c>
+      <c r="AC9">
+        <v>47.3115102576017</v>
       </c>
     </row>
   </sheetData>
